--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/151.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/151.xlsx
@@ -426,13 +426,13 @@
         <v>-14.40292686973127</v>
       </c>
       <c r="E2">
-        <v>-13.9570313138682</v>
+        <v>-14.79310182603546</v>
       </c>
       <c r="F2">
-        <v>4.118568854772785</v>
+        <v>3.145187454439198</v>
       </c>
       <c r="G2">
-        <v>-12.70970851274324</v>
+        <v>-11.29528672098809</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.15776664619096</v>
       </c>
       <c r="E3">
-        <v>-14.19668822015611</v>
+        <v>-14.70985070502928</v>
       </c>
       <c r="F3">
-        <v>4.100522042535395</v>
+        <v>3.123610140331076</v>
       </c>
       <c r="G3">
-        <v>-11.63041625579864</v>
+        <v>-10.27948516175477</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.87368335730273</v>
       </c>
       <c r="E4">
-        <v>-15.73711430053502</v>
+        <v>-14.80612629675013</v>
       </c>
       <c r="F4">
-        <v>4.227060133517436</v>
+        <v>3.236844650824158</v>
       </c>
       <c r="G4">
-        <v>-11.05019001877437</v>
+        <v>-10.02682904857749</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.57463033244209</v>
       </c>
       <c r="E5">
-        <v>-15.73235887356809</v>
+        <v>-15.91605125725393</v>
       </c>
       <c r="F5">
-        <v>4.273781711770134</v>
+        <v>3.398028380060885</v>
       </c>
       <c r="G5">
-        <v>-10.78956330236042</v>
+        <v>-9.868016149727772</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.28038046358891</v>
       </c>
       <c r="E6">
-        <v>-15.39564557183026</v>
+        <v>-16.46940021490613</v>
       </c>
       <c r="F6">
-        <v>4.62776298380403</v>
+        <v>4.01601200010179</v>
       </c>
       <c r="G6">
-        <v>-10.71966322667795</v>
+        <v>-9.302585002301344</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.01343665192904</v>
       </c>
       <c r="E7">
-        <v>-17.7854365938272</v>
+        <v>-17.01312202870739</v>
       </c>
       <c r="F7">
-        <v>4.09489245766597</v>
+        <v>3.697802945990387</v>
       </c>
       <c r="G7">
-        <v>-10.59033346649568</v>
+        <v>-9.082872569747023</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.76673665502114</v>
       </c>
       <c r="E8">
-        <v>-17.80841215887616</v>
+        <v>-17.59720475016332</v>
       </c>
       <c r="F8">
-        <v>3.962100192792792</v>
+        <v>3.889798629141646</v>
       </c>
       <c r="G8">
-        <v>-10.37577072764733</v>
+        <v>-8.653953340873022</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.5575408632558</v>
       </c>
       <c r="E9">
-        <v>-17.99756601545415</v>
+        <v>-18.2590937325786</v>
       </c>
       <c r="F9">
-        <v>4.82623650004518</v>
+        <v>4.082630963369732</v>
       </c>
       <c r="G9">
-        <v>-10.25328242366606</v>
+        <v>-8.826355165319482</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.36637166517071</v>
       </c>
       <c r="E10">
-        <v>-18.24459902505495</v>
+        <v>-18.40668225021771</v>
       </c>
       <c r="F10">
-        <v>4.640082463818464</v>
+        <v>4.590050729424179</v>
       </c>
       <c r="G10">
-        <v>-10.2799485689197</v>
+        <v>-8.746412860567299</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.19897276552179</v>
       </c>
       <c r="E11">
-        <v>-19.80265548750775</v>
+        <v>-19.6888325779395</v>
       </c>
       <c r="F11">
-        <v>5.282968464722327</v>
+        <v>4.890383614983168</v>
       </c>
       <c r="G11">
-        <v>-8.658161861153896</v>
+        <v>-8.372092133327248</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.05096309941008</v>
       </c>
       <c r="E12">
-        <v>-20.54295709973579</v>
+        <v>-20.51370603237502</v>
       </c>
       <c r="F12">
-        <v>5.991469447601938</v>
+        <v>4.87383449101004</v>
       </c>
       <c r="G12">
-        <v>-10.16837839881847</v>
+        <v>-8.284052604225726</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.91567918344955</v>
       </c>
       <c r="E13">
-        <v>-20.67726780076942</v>
+        <v>-20.95137559499678</v>
       </c>
       <c r="F13">
-        <v>5.467656290646087</v>
+        <v>5.311303600102486</v>
       </c>
       <c r="G13">
-        <v>-9.144192433330796</v>
+        <v>-7.994703781192642</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.81167850685173</v>
       </c>
       <c r="E14">
-        <v>-21.5243484761588</v>
+        <v>-22.0935543946492</v>
       </c>
       <c r="F14">
-        <v>5.919780875828864</v>
+        <v>5.700248603473744</v>
       </c>
       <c r="G14">
-        <v>-10.20764530284111</v>
+        <v>-7.773825651178388</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.72770654714416</v>
       </c>
       <c r="E15">
-        <v>-23.26151217699483</v>
+        <v>-23.33806416813407</v>
       </c>
       <c r="F15">
-        <v>6.732608106151851</v>
+        <v>6.216515333390091</v>
       </c>
       <c r="G15">
-        <v>-8.413562505784787</v>
+        <v>-7.884394600728923</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.67771500086082</v>
       </c>
       <c r="E16">
-        <v>-24.15539123759238</v>
+        <v>-22.88730368341646</v>
       </c>
       <c r="F16">
-        <v>6.718171319055861</v>
+        <v>6.650515239799613</v>
       </c>
       <c r="G16">
-        <v>-8.884136164610002</v>
+        <v>-8.004389643625672</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.64761079310092</v>
       </c>
       <c r="E17">
-        <v>-24.35770246764743</v>
+        <v>-24.16267181704481</v>
       </c>
       <c r="F17">
-        <v>7.353310428008743</v>
+        <v>6.929573993719906</v>
       </c>
       <c r="G17">
-        <v>-8.53920328385982</v>
+        <v>-8.081163809816539</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.63142169474607</v>
       </c>
       <c r="E18">
-        <v>-24.23216750214316</v>
+        <v>-24.90667809377459</v>
       </c>
       <c r="F18">
-        <v>7.86670106630257</v>
+        <v>7.496009967019402</v>
       </c>
       <c r="G18">
-        <v>-7.543332148835066</v>
+        <v>-7.551587323232165</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.62325194990488</v>
       </c>
       <c r="E19">
-        <v>-26.49792702113542</v>
+        <v>-25.95913506917674</v>
       </c>
       <c r="F19">
-        <v>7.509079947900773</v>
+        <v>7.979653931878699</v>
       </c>
       <c r="G19">
-        <v>-7.237577406791424</v>
+        <v>-7.618853157622199</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.59991959287227</v>
       </c>
       <c r="E20">
-        <v>-27.35523290280653</v>
+        <v>-26.15220955724537</v>
       </c>
       <c r="F20">
-        <v>8.482391765372524</v>
+        <v>8.183632777878854</v>
       </c>
       <c r="G20">
-        <v>-7.787640406182264</v>
+        <v>-7.131150403534691</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.5644774873338</v>
       </c>
       <c r="E21">
-        <v>-26.99999212534865</v>
+        <v>-27.63521749105852</v>
       </c>
       <c r="F21">
-        <v>8.63969542169454</v>
+        <v>8.550125711164634</v>
       </c>
       <c r="G21">
-        <v>-6.692952588383872</v>
+        <v>-6.283600890220264</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.49740456689827</v>
       </c>
       <c r="E22">
-        <v>-27.40148721733115</v>
+        <v>-27.06957502788482</v>
       </c>
       <c r="F22">
-        <v>9.203710905443055</v>
+        <v>8.814404733884178</v>
       </c>
       <c r="G22">
-        <v>-7.223917991090719</v>
+        <v>-6.451871211351289</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.40308244347037</v>
       </c>
       <c r="E23">
-        <v>-28.03460690489933</v>
+        <v>-27.4085725958513</v>
       </c>
       <c r="F23">
-        <v>9.1589840358963</v>
+        <v>9.171677937976799</v>
       </c>
       <c r="G23">
-        <v>-7.128059281938812</v>
+        <v>-5.882958636012611</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.28067633389511</v>
       </c>
       <c r="E24">
-        <v>-28.45963201564265</v>
+        <v>-28.7051262604476</v>
       </c>
       <c r="F24">
-        <v>9.601721561670551</v>
+        <v>9.19694480049699</v>
       </c>
       <c r="G24">
-        <v>-6.505767422690232</v>
+        <v>-5.661207211932631</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.12682034577883</v>
       </c>
       <c r="E25">
-        <v>-31.39247618441755</v>
+        <v>-28.70737730098566</v>
       </c>
       <c r="F25">
-        <v>9.551845560347992</v>
+        <v>9.348275927844821</v>
       </c>
       <c r="G25">
-        <v>-5.767827410289106</v>
+        <v>-5.598416193771765</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.95999997289656</v>
       </c>
       <c r="E26">
-        <v>-28.67106162116136</v>
+        <v>-28.58339563651688</v>
       </c>
       <c r="F26">
-        <v>9.89063291747974</v>
+        <v>9.060071997797621</v>
       </c>
       <c r="G26">
-        <v>-6.264171728973199</v>
+        <v>-5.917618881204231</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.77528226990652</v>
       </c>
       <c r="E27">
-        <v>-29.41996453404312</v>
+        <v>-29.22847034288359</v>
       </c>
       <c r="F27">
-        <v>9.249024259110994</v>
+        <v>9.104068247295109</v>
       </c>
       <c r="G27">
-        <v>-6.437128336645273</v>
+        <v>-5.745677853178101</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.58877241556971</v>
       </c>
       <c r="E28">
-        <v>-28.65140654856661</v>
+        <v>-29.77962848156195</v>
       </c>
       <c r="F28">
-        <v>9.658671820613018</v>
+        <v>8.921563997845126</v>
       </c>
       <c r="G28">
-        <v>-6.079767006269095</v>
+        <v>-5.403701640677354</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.39726782036159</v>
       </c>
       <c r="E29">
-        <v>-28.26523472976707</v>
+        <v>-29.15556071807622</v>
       </c>
       <c r="F29">
-        <v>9.400567448513941</v>
+        <v>8.598919864659136</v>
       </c>
       <c r="G29">
-        <v>-5.792313583809158</v>
+        <v>-5.2847952782751</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.20181154529463</v>
       </c>
       <c r="E30">
-        <v>-28.33009543102691</v>
+        <v>-29.25382569802166</v>
       </c>
       <c r="F30">
-        <v>9.122875500808268</v>
+        <v>8.877948797352929</v>
       </c>
       <c r="G30">
-        <v>-5.30738082973282</v>
+        <v>-4.884850092873273</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.00614049770912</v>
       </c>
       <c r="E31">
-        <v>-28.01481685293653</v>
+        <v>-28.94973171802904</v>
       </c>
       <c r="F31">
-        <v>8.333030495708551</v>
+        <v>8.046037638804245</v>
       </c>
       <c r="G31">
-        <v>-5.091918689372832</v>
+        <v>-4.501621505088345</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.794194134177596</v>
       </c>
       <c r="E32">
-        <v>-28.51535149877655</v>
+        <v>-28.70705750371365</v>
       </c>
       <c r="F32">
-        <v>7.781573061786475</v>
+        <v>8.065403211946892</v>
       </c>
       <c r="G32">
-        <v>-4.783540149015122</v>
+        <v>-4.063961503323296</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.568881725096547</v>
       </c>
       <c r="E33">
-        <v>-27.66324336107847</v>
+        <v>-28.56631555494352</v>
       </c>
       <c r="F33">
-        <v>7.727502207936141</v>
+        <v>7.546987696987683</v>
       </c>
       <c r="G33">
-        <v>-4.883936332266384</v>
+        <v>-4.036300664380451</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.313297230065539</v>
       </c>
       <c r="E34">
-        <v>-27.62794521802875</v>
+        <v>-28.34112013048867</v>
       </c>
       <c r="F34">
-        <v>8.281559058768201</v>
+        <v>7.631000718979609</v>
       </c>
       <c r="G34">
-        <v>-5.491626297016867</v>
+        <v>-3.722324687619393</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.025371183310105</v>
       </c>
       <c r="E35">
-        <v>-27.82041749045528</v>
+        <v>-27.95784725319385</v>
       </c>
       <c r="F35">
-        <v>7.859625151947856</v>
+        <v>7.188828139774067</v>
       </c>
       <c r="G35">
-        <v>-4.729116567268774</v>
+        <v>-3.986508543538738</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.703220707231957</v>
       </c>
       <c r="E36">
-        <v>-28.73931341946793</v>
+        <v>-27.40130032282153</v>
       </c>
       <c r="F36">
-        <v>7.934716657011632</v>
+        <v>7.261517379369724</v>
       </c>
       <c r="G36">
-        <v>-5.064169085113889</v>
+        <v>-3.079919652040876</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.340887868183726</v>
       </c>
       <c r="E37">
-        <v>-26.05190535053944</v>
+        <v>-26.50313099492544</v>
       </c>
       <c r="F37">
-        <v>8.413145220702903</v>
+        <v>7.231835318592612</v>
       </c>
       <c r="G37">
-        <v>-3.753209796132264</v>
+        <v>-2.385145690709217</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.955949669358813</v>
       </c>
       <c r="E38">
-        <v>-26.49887395331749</v>
+        <v>-26.7340993831218</v>
       </c>
       <c r="F38">
-        <v>7.589781157016306</v>
+        <v>6.792325112219667</v>
       </c>
       <c r="G38">
-        <v>-3.291423903600737</v>
+        <v>-2.032251344328435</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.550633545315379</v>
       </c>
       <c r="E39">
-        <v>-27.57621281776668</v>
+        <v>-27.13287412168654</v>
       </c>
       <c r="F39">
-        <v>8.331441687029981</v>
+        <v>6.691746398906557</v>
       </c>
       <c r="G39">
-        <v>-3.835847694674773</v>
+        <v>-1.796696913595238</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.146671693211991</v>
       </c>
       <c r="E40">
-        <v>-27.14300795731912</v>
+        <v>-25.75175276809408</v>
       </c>
       <c r="F40">
-        <v>7.671580781307951</v>
+        <v>6.681907050896104</v>
       </c>
       <c r="G40">
-        <v>-3.53334855113625</v>
+        <v>-1.17687220798526</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.755250824663179</v>
       </c>
       <c r="E41">
-        <v>-26.33406206831431</v>
+        <v>-26.29524615527247</v>
       </c>
       <c r="F41">
-        <v>7.725477678003699</v>
+        <v>6.763655316408776</v>
       </c>
       <c r="G41">
-        <v>-2.435251100901864</v>
+        <v>-1.034625788938453</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.387446379930777</v>
       </c>
       <c r="E42">
-        <v>-26.41673173973503</v>
+        <v>-25.23246014330547</v>
       </c>
       <c r="F42">
-        <v>6.887410092917411</v>
+        <v>6.836347869474044</v>
       </c>
       <c r="G42">
-        <v>-2.514335776055868</v>
+        <v>-0.4119475394903873</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.059276887759402</v>
       </c>
       <c r="E43">
-        <v>-26.67580490896651</v>
+        <v>-25.59229437248861</v>
       </c>
       <c r="F43">
-        <v>7.378671724412852</v>
+        <v>6.683408052629977</v>
       </c>
       <c r="G43">
-        <v>-3.506510096739605</v>
+        <v>-0.3458565401663545</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.76894885803348</v>
       </c>
       <c r="E44">
-        <v>-24.00864997506354</v>
+        <v>-24.76394883338553</v>
       </c>
       <c r="F44">
-        <v>7.679511570822354</v>
+        <v>6.688267255814798</v>
       </c>
       <c r="G44">
-        <v>-2.652942817142663</v>
+        <v>-0.4860013098173157</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.528126965579164</v>
       </c>
       <c r="E45">
-        <v>-25.49711522855752</v>
+        <v>-24.28355103265394</v>
       </c>
       <c r="F45">
-        <v>7.228493684489719</v>
+        <v>6.666096830646272</v>
       </c>
       <c r="G45">
-        <v>-2.223088941705043</v>
+        <v>0.1537016051093994</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.330102954069402</v>
       </c>
       <c r="E46">
-        <v>-23.84389208180759</v>
+        <v>-24.23423995459425</v>
       </c>
       <c r="F46">
-        <v>7.32831526999667</v>
+        <v>6.562317305688745</v>
       </c>
       <c r="G46">
-        <v>-2.427497189466257</v>
+        <v>0.5144804001553444</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.176466765634208</v>
       </c>
       <c r="E47">
-        <v>-24.13310925883468</v>
+        <v>-24.4893758794898</v>
       </c>
       <c r="F47">
-        <v>7.052149175046954</v>
+        <v>6.565451847940938</v>
       </c>
       <c r="G47">
-        <v>-1.086362914500545</v>
+        <v>0.589740334483367</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.064806263731645</v>
       </c>
       <c r="E48">
-        <v>-22.79772306835123</v>
+        <v>-23.78481680392323</v>
       </c>
       <c r="F48">
-        <v>7.47880311932845</v>
+        <v>5.939350227352599</v>
       </c>
       <c r="G48">
-        <v>-2.455416492123623</v>
+        <v>0.447433868310964</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.984481819861935</v>
       </c>
       <c r="E49">
-        <v>-22.7783981760568</v>
+        <v>-22.9304846215607</v>
       </c>
       <c r="F49">
-        <v>6.634507868107916</v>
+        <v>6.497978009513307</v>
       </c>
       <c r="G49">
-        <v>-0.6506035347978261</v>
+        <v>1.261122024278651</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.937668913286204</v>
       </c>
       <c r="E50">
-        <v>-22.04272739445595</v>
+        <v>-23.16138240516454</v>
       </c>
       <c r="F50">
-        <v>7.154785552988619</v>
+        <v>6.032150570753422</v>
       </c>
       <c r="G50">
-        <v>-2.387973127101393</v>
+        <v>0.8463660848114386</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.911250230227966</v>
       </c>
       <c r="E51">
-        <v>-22.43272224428</v>
+        <v>-22.68725595353344</v>
       </c>
       <c r="F51">
-        <v>7.72205155042572</v>
+        <v>5.84618705902935</v>
       </c>
       <c r="G51">
-        <v>-1.651816253255998</v>
+        <v>1.32994908393417</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.906345594097183</v>
       </c>
       <c r="E52">
-        <v>-21.83841431654233</v>
+        <v>-22.59952767071909</v>
       </c>
       <c r="F52">
-        <v>7.181475550706819</v>
+        <v>5.765290355206756</v>
       </c>
       <c r="G52">
-        <v>-2.231699177366534</v>
+        <v>0.921114313199603</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.915752532348104</v>
       </c>
       <c r="E53">
-        <v>-21.10033467237308</v>
+        <v>-22.47712007334242</v>
       </c>
       <c r="F53">
-        <v>6.950327910629644</v>
+        <v>5.783771231963213</v>
       </c>
       <c r="G53">
-        <v>-1.619497845962606</v>
+        <v>1.321579036775061</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.936365830877618</v>
       </c>
       <c r="E54">
-        <v>-20.52361559459606</v>
+        <v>-21.52700237819537</v>
       </c>
       <c r="F54">
-        <v>6.812134690290214</v>
+        <v>5.883259813774239</v>
       </c>
       <c r="G54">
-        <v>-2.405151826510919</v>
+        <v>1.07403084539029</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.970343260492382</v>
       </c>
       <c r="E55">
-        <v>-21.17813678012109</v>
+        <v>-21.86852509864734</v>
       </c>
       <c r="F55">
-        <v>6.68719369166077</v>
+        <v>5.595254691903713</v>
       </c>
       <c r="G55">
-        <v>-1.470531370338273</v>
+        <v>0.7401296659098567</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.011109645023895</v>
       </c>
       <c r="E56">
-        <v>-20.78389734832307</v>
+        <v>-21.3729971490594</v>
       </c>
       <c r="F56">
-        <v>6.93597561700874</v>
+        <v>5.982519766182093</v>
       </c>
       <c r="G56">
-        <v>-1.977209016113993</v>
+        <v>1.292247321293903</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.064855253696077</v>
       </c>
       <c r="E57">
-        <v>-19.90279771897202</v>
+        <v>-21.74748390779654</v>
       </c>
       <c r="F57">
-        <v>6.851516933354108</v>
+        <v>5.779816605982248</v>
       </c>
       <c r="G57">
-        <v>-1.996880976608032</v>
+        <v>0.3821260923642652</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.125250711113482</v>
       </c>
       <c r="E58">
-        <v>-19.69431481688828</v>
+        <v>-21.5412437398282</v>
       </c>
       <c r="F58">
-        <v>6.720568614319562</v>
+        <v>5.942918834123859</v>
       </c>
       <c r="G58">
-        <v>-1.918921532372798</v>
+        <v>0.3610887124490744</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.195755992943647</v>
       </c>
       <c r="E59">
-        <v>-20.92133957069562</v>
+        <v>-20.53019012812327</v>
       </c>
       <c r="F59">
-        <v>6.128716672367371</v>
+        <v>5.590012782978797</v>
       </c>
       <c r="G59">
-        <v>-2.622303118621357</v>
+        <v>-0.007049771599218949</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.275018257613248</v>
       </c>
       <c r="E60">
-        <v>-20.72197296746987</v>
+        <v>-21.20126186077774</v>
       </c>
       <c r="F60">
-        <v>6.690879926603229</v>
+        <v>6.118494618616825</v>
       </c>
       <c r="G60">
-        <v>-2.339146981758393</v>
+        <v>0.479073482010666</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.35652446967661</v>
       </c>
       <c r="E61">
-        <v>-19.02404050080817</v>
+        <v>-20.91082779283248</v>
       </c>
       <c r="F61">
-        <v>6.330995708456983</v>
+        <v>5.887080244235951</v>
       </c>
       <c r="G61">
-        <v>-1.778698440384104</v>
+        <v>-0.02535892341669642</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.441096766280578</v>
       </c>
       <c r="E62">
-        <v>-19.33460518404488</v>
+        <v>-21.06538539907465</v>
       </c>
       <c r="F62">
-        <v>6.985167386856586</v>
+        <v>5.836258247339395</v>
       </c>
       <c r="G62">
-        <v>-3.04149210240428</v>
+        <v>-0.5079002354475739</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.516944859053936</v>
       </c>
       <c r="E63">
-        <v>-19.84600670731631</v>
+        <v>-21.04566595170436</v>
       </c>
       <c r="F63">
-        <v>6.860728378873238</v>
+        <v>5.777256950707597</v>
       </c>
       <c r="G63">
-        <v>-2.964830198230829</v>
+        <v>-0.8558419993390148</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.584379563351876</v>
       </c>
       <c r="E64">
-        <v>-19.21198992610196</v>
+        <v>-20.32159508933375</v>
       </c>
       <c r="F64">
-        <v>6.921586875222113</v>
+        <v>5.819409254366454</v>
       </c>
       <c r="G64">
-        <v>-2.907302441165648</v>
+        <v>-0.8912645819512399</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.636497260946617</v>
       </c>
       <c r="E65">
-        <v>-20.06750992690339</v>
+        <v>-20.34504827368506</v>
       </c>
       <c r="F65">
-        <v>6.428095278678335</v>
+        <v>5.740296853929489</v>
       </c>
       <c r="G65">
-        <v>-3.173828134983221</v>
+        <v>-0.8796154395856924</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.670605093002323</v>
       </c>
       <c r="E66">
-        <v>-21.82075486198917</v>
+        <v>-20.60628526601678</v>
       </c>
       <c r="F66">
-        <v>5.835610464030406</v>
+        <v>5.933828330245538</v>
       </c>
       <c r="G66">
-        <v>-2.869866974473675</v>
+        <v>-1.106711057843682</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.689523899145682</v>
       </c>
       <c r="E67">
-        <v>-20.37219781611547</v>
+        <v>-19.92381712148698</v>
       </c>
       <c r="F67">
-        <v>6.227640307609689</v>
+        <v>5.462064810677191</v>
       </c>
       <c r="G67">
-        <v>-2.033916999377565</v>
+        <v>-1.201716053514294</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.688908492009892</v>
       </c>
       <c r="E68">
-        <v>-18.05826104575519</v>
+        <v>-19.22912192281688</v>
       </c>
       <c r="F68">
-        <v>6.321174584529392</v>
+        <v>5.719446846401025</v>
       </c>
       <c r="G68">
-        <v>-2.984940763816175</v>
+        <v>-1.427845696273571</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.677474588587353</v>
       </c>
       <c r="E69">
-        <v>-17.14411016068116</v>
+        <v>-19.75527149950278</v>
       </c>
       <c r="F69">
-        <v>5.475290524630288</v>
+        <v>5.672120559944284</v>
       </c>
       <c r="G69">
-        <v>-2.424497443931068</v>
+        <v>-1.221074724657399</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.652394322464781</v>
       </c>
       <c r="E70">
-        <v>-18.08075483829046</v>
+        <v>-19.70904625745744</v>
       </c>
       <c r="F70">
-        <v>5.437533538410687</v>
+        <v>5.680768715629511</v>
       </c>
       <c r="G70">
-        <v>-2.695983552471756</v>
+        <v>-1.202347853705343</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.618589160296144</v>
       </c>
       <c r="E71">
-        <v>-17.91414876599497</v>
+        <v>-19.58576648570256</v>
       </c>
       <c r="F71">
-        <v>6.404503375046605</v>
+        <v>5.716395140889112</v>
       </c>
       <c r="G71">
-        <v>-2.845615767966823</v>
+        <v>-1.562920399928591</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.577928238712335</v>
       </c>
       <c r="E72">
-        <v>-17.609411038247</v>
+        <v>-19.32926415428114</v>
       </c>
       <c r="F72">
-        <v>6.130515886366252</v>
+        <v>5.480063577605219</v>
       </c>
       <c r="G72">
-        <v>-2.322892485934121</v>
+        <v>-0.9250946103628859</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.527474814561152</v>
       </c>
       <c r="E73">
-        <v>-18.5849131610114</v>
+        <v>-20.21204998743008</v>
       </c>
       <c r="F73">
-        <v>5.847222518282849</v>
+        <v>5.463628768333677</v>
       </c>
       <c r="G73">
-        <v>-2.290038875999552</v>
+        <v>-0.8560378051833484</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.474239345843547</v>
       </c>
       <c r="E74">
-        <v>-19.42100028602396</v>
+        <v>-19.70427837085654</v>
       </c>
       <c r="F74">
-        <v>5.528816312729581</v>
+        <v>5.249504078384033</v>
       </c>
       <c r="G74">
-        <v>-2.249961335781371</v>
+        <v>-1.075739794759305</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.413039063030818</v>
       </c>
       <c r="E75">
-        <v>-19.1578486632715</v>
+        <v>-20.31696425870657</v>
       </c>
       <c r="F75">
-        <v>5.537603634138478</v>
+        <v>5.503231357126715</v>
       </c>
       <c r="G75">
-        <v>-1.942462616350867</v>
+        <v>-1.118459408503691</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.348582462957371</v>
       </c>
       <c r="E76">
-        <v>-17.34789993396784</v>
+        <v>-19.69078043405085</v>
       </c>
       <c r="F76">
-        <v>5.804399237027726</v>
+        <v>5.243017961620112</v>
       </c>
       <c r="G76">
-        <v>-2.542150648929588</v>
+        <v>-0.7393166360038556</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.278743810475429</v>
       </c>
       <c r="E77">
-        <v>-18.97344192723779</v>
+        <v>-19.81389407735274</v>
       </c>
       <c r="F77">
-        <v>5.391047216500384</v>
+        <v>5.035546718649754</v>
       </c>
       <c r="G77">
-        <v>-1.925148158222603</v>
+        <v>-0.7112198027142944</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.200786795398362</v>
       </c>
       <c r="E78">
-        <v>-20.44445538674483</v>
+        <v>-20.77123836020499</v>
       </c>
       <c r="F78">
-        <v>5.355815094124515</v>
+        <v>4.554729143368808</v>
       </c>
       <c r="G78">
-        <v>-1.088759578035187</v>
+        <v>-0.2177446923358344</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.117806470928697</v>
       </c>
       <c r="E79">
-        <v>-19.44064082237907</v>
+        <v>-20.84592971267071</v>
       </c>
       <c r="F79">
-        <v>4.760798788693631</v>
+        <v>4.555163207887875</v>
       </c>
       <c r="G79">
-        <v>-1.773012238664659</v>
+        <v>0.5293773087922368</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.022676419502867</v>
       </c>
       <c r="E80">
-        <v>-18.30373244789786</v>
+        <v>-21.00250577961674</v>
       </c>
       <c r="F80">
-        <v>4.710979116354463</v>
+        <v>4.560164890265979</v>
       </c>
       <c r="G80">
-        <v>-0.9057516036873275</v>
+        <v>0.624468459034356</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.918967040756009</v>
       </c>
       <c r="E81">
-        <v>-22.37522103348775</v>
+        <v>-21.22960337485837</v>
       </c>
       <c r="F81">
-        <v>5.555908897005541</v>
+        <v>4.390170645333075</v>
       </c>
       <c r="G81">
-        <v>-0.5532567012289851</v>
+        <v>0.8419591479416394</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.80158387835485</v>
       </c>
       <c r="E82">
-        <v>-21.52488839363103</v>
+        <v>-22.0717915673071</v>
       </c>
       <c r="F82">
-        <v>3.573252936775065</v>
+        <v>4.464841339756228</v>
       </c>
       <c r="G82">
-        <v>-0.2006756441991358</v>
+        <v>0.3485284202212283</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.672141960832928</v>
       </c>
       <c r="E83">
-        <v>-22.10794527188973</v>
+        <v>-23.0637694793971</v>
       </c>
       <c r="F83">
-        <v>4.022165113169784</v>
+        <v>4.273904310145748</v>
       </c>
       <c r="G83">
-        <v>-0.0660917605272459</v>
+        <v>1.201257650804423</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.533215481354155</v>
       </c>
       <c r="E84">
-        <v>-24.30753582805482</v>
+        <v>-23.64913138994108</v>
       </c>
       <c r="F84">
-        <v>4.794624343219546</v>
+        <v>3.889016650313403</v>
       </c>
       <c r="G84">
-        <v>-0.2980642496814347</v>
+        <v>1.030118121367765</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.381810132648631</v>
       </c>
       <c r="E85">
-        <v>-23.17811569359228</v>
+        <v>-24.13775670230716</v>
       </c>
       <c r="F85">
-        <v>4.294066772729888</v>
+        <v>4.016176016847544</v>
       </c>
       <c r="G85">
-        <v>0.577963265632855</v>
+        <v>0.9897977819026114</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.224770197577874</v>
       </c>
       <c r="E86">
-        <v>-23.96889543626228</v>
+        <v>-25.14633915327382</v>
       </c>
       <c r="F86">
-        <v>4.696172877396824</v>
+        <v>3.664941611121331</v>
       </c>
       <c r="G86">
-        <v>0.3553085239243495</v>
+        <v>1.547674739854654</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.059561298893306</v>
       </c>
       <c r="E87">
-        <v>-24.09516136695972</v>
+        <v>-26.48956660673855</v>
       </c>
       <c r="F87">
-        <v>3.379347038392951</v>
+        <v>3.174148835575874</v>
       </c>
       <c r="G87">
-        <v>-0.4157540051042305</v>
+        <v>1.066363088526191</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.89161367639607</v>
       </c>
       <c r="E88">
-        <v>-26.84223654638636</v>
+        <v>-27.45277522398145</v>
       </c>
       <c r="F88">
-        <v>3.427405601633767</v>
+        <v>2.817891209919085</v>
       </c>
       <c r="G88">
-        <v>0.6790121350318947</v>
+        <v>1.552833571166694</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.723016972023951</v>
       </c>
       <c r="E89">
-        <v>-25.9255729684608</v>
+        <v>-28.34098722772627</v>
       </c>
       <c r="F89">
-        <v>3.63795837134254</v>
+        <v>2.878832543008239</v>
       </c>
       <c r="G89">
-        <v>0.3876608708974254</v>
+        <v>1.473263297518743</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.554459599797326</v>
       </c>
       <c r="E90">
-        <v>-28.33046922004615</v>
+        <v>-28.98456262480472</v>
       </c>
       <c r="F90">
-        <v>3.242214128329104</v>
+        <v>2.611531636003284</v>
       </c>
       <c r="G90">
-        <v>0.7739596943215027</v>
+        <v>1.72591549457914</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.393853483733377</v>
       </c>
       <c r="E91">
-        <v>-30.87268102105863</v>
+        <v>-31.04610043653251</v>
       </c>
       <c r="F91">
-        <v>2.638548010478187</v>
+        <v>2.202447364335165</v>
       </c>
       <c r="G91">
-        <v>0.06939021928398695</v>
+        <v>1.671959236114602</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.240619467079516</v>
       </c>
       <c r="E92">
-        <v>-30.76701917174367</v>
+        <v>-32.17982122132192</v>
       </c>
       <c r="F92">
-        <v>2.757151998476215</v>
+        <v>1.909780190721682</v>
       </c>
       <c r="G92">
-        <v>-1.232726477767538</v>
+        <v>1.173142542302724</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.103844498252869</v>
       </c>
       <c r="E93">
-        <v>-32.61351616070581</v>
+        <v>-33.33108101753608</v>
       </c>
       <c r="F93">
-        <v>3.334321956581187</v>
+        <v>1.760814880676247</v>
       </c>
       <c r="G93">
-        <v>0.5007531050952707</v>
+        <v>1.286036359911645</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.985507612632524</v>
       </c>
       <c r="E94">
-        <v>-32.9000648994567</v>
+        <v>-36.28083290961435</v>
       </c>
       <c r="F94">
-        <v>1.659820326926932</v>
+        <v>1.485506974355832</v>
       </c>
       <c r="G94">
-        <v>0.4391499757233616</v>
+        <v>1.569390913363534</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.89111159861017</v>
       </c>
       <c r="E95">
-        <v>-36.57915392586546</v>
+        <v>-37.71924781343282</v>
       </c>
       <c r="F95">
-        <v>1.531179839476585</v>
+        <v>1.133411066530707</v>
       </c>
       <c r="G95">
-        <v>-1.045953809719293</v>
+        <v>1.093444342169809</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.827334540571922</v>
       </c>
       <c r="E96">
-        <v>-39.88232541223569</v>
+        <v>-39.54818710151925</v>
       </c>
       <c r="F96">
-        <v>1.342053621008624</v>
+        <v>1.027751147568825</v>
       </c>
       <c r="G96">
-        <v>0.726517243611792</v>
+        <v>1.233455963846623</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.790733626089135</v>
       </c>
       <c r="E97">
-        <v>-39.25168519182842</v>
+        <v>-41.59903454729694</v>
       </c>
       <c r="F97">
-        <v>0.8636615054830764</v>
+        <v>0.0521903125984723</v>
       </c>
       <c r="G97">
-        <v>-1.683085141223762</v>
+        <v>0.7903342843969652</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.78868638895254</v>
       </c>
       <c r="E98">
-        <v>-43.6117056745768</v>
+        <v>-43.39063646557316</v>
       </c>
       <c r="F98">
-        <v>0.7306107899802254</v>
+        <v>-0.05552809935936701</v>
       </c>
       <c r="G98">
-        <v>-0.4283873981806277</v>
+        <v>0.2234894187744486</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.808723804958778</v>
       </c>
       <c r="E99">
-        <v>-45.67093741571648</v>
+        <v>-45.14623834808577</v>
       </c>
       <c r="F99">
-        <v>0.3388609345830888</v>
+        <v>0.03556497882428622</v>
       </c>
       <c r="G99">
-        <v>-0.9862486916651234</v>
+        <v>-0.5994355515565968</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.856165082295059</v>
       </c>
       <c r="E100">
-        <v>-47.11207371125554</v>
+        <v>-46.96089889563745</v>
       </c>
       <c r="F100">
-        <v>0.2997073209223674</v>
+        <v>-0.4777767857927758</v>
       </c>
       <c r="G100">
-        <v>-0.9577263070072108</v>
+        <v>-0.1634307618623136</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.908057327930188</v>
       </c>
       <c r="E101">
-        <v>-48.5897385386993</v>
+        <v>-49.32302953021103</v>
       </c>
       <c r="F101">
-        <v>-0.6861053890250318</v>
+        <v>-0.6845563419817968</v>
       </c>
       <c r="G101">
-        <v>-2.263474549784974</v>
+        <v>-0.5311280300747088</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.977379199801435</v>
       </c>
       <c r="E102">
-        <v>-51.2886987649278</v>
+        <v>-51.09549448900528</v>
       </c>
       <c r="F102">
-        <v>-0.4855899471359807</v>
+        <v>-1.023294825436779</v>
       </c>
       <c r="G102">
-        <v>-3.168705854095457</v>
+        <v>-1.064265572281362</v>
       </c>
     </row>
   </sheetData>
